--- a/outputs/monitor_xlsx/20260304.xlsx
+++ b/outputs/monitor_xlsx/20260304.xlsx
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2328,7 +2328,7 @@
         <v>-106283</v>
       </c>
       <c r="N23" t="n">
-        <v>18.25</v>
+        <v>12.24</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2386,6 +2386,59 @@
       <c r="O24" t="inlineStr">
         <is>
           <t>偏多</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4525</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="E25" t="n">
+        <v>343</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-52</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-27</v>
+      </c>
+      <c r="J25" t="n">
+        <v>18</v>
+      </c>
+      <c r="K25" t="n">
+        <v>331</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1595</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-8887</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-5</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>主力積極賣出</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260304.xlsx
+++ b/outputs/monitor_xlsx/20260304.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -526,215 +526,232 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>美債10年殖利率</t>
+          <t>加權指數 (TWII)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.08%</t>
+          <t>32828.88</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+0.59%</t>
-        </is>
-      </c>
+          <t>-4.35%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>黃金指數 (GC=F)</t>
+          <t>櫃買指數 (OTC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5182.3$</t>
+          <t>293.8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+1.47%</t>
-        </is>
-      </c>
+          <t>-4.86%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>貨幣</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>美元/台幣匯率</t>
+          <t>台指近月期貨</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.73</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+0.62%</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>現貨</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>費半指數 (SOX)</t>
+          <t>美債10年殖利率</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7914.48</t>
+          <t>4.08%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+1.93%</t>
-        </is>
-      </c>
+          <t>+0.59%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>情緒</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>恐慌指數 (VIX)</t>
+          <t>黃金指數 (GC=F)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>5120.2$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-10.27%</t>
-        </is>
-      </c>
+          <t>+0.25%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>貨幣</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>外資現貨</t>
+          <t>美元/台幣匯率</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-966.15億</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>-399.46億</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-1997.28億</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-43.44億</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-868.84億</t>
-        </is>
-      </c>
+          <t>31.73</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+0.62%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>現貨</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>投信現貨</t>
+          <t>費半指數 (SOX)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>67.64億</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>46.14億</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>230.69億</t>
-        </is>
-      </c>
+          <t>7914.48</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>+1.93%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>情緒</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>選擇權 P/C Ratio</t>
+          <t>恐慌指數 (VIX)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>133.33%</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>145.37%</t>
-        </is>
-      </c>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-10.27%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>原物料</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>三大法人合計</t>
+          <t>WTI原油期貨</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1298.54億</t>
-        </is>
-      </c>
+          <t>74.66$</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>+0.13%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -744,54 +761,175 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>外資期貨未平倉</t>
+          <t>外資現貨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>32058口</t>
-        </is>
-      </c>
+          <t>-966.15億</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>17022口</t>
+          <t>-146.35億</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-731.75億</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>None億</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>None億</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>投信現貨</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>67.64億</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>30.25億</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>151.27億</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>選擇權 P/C Ratio</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>None%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>三大法人合計</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-1298.54億</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>外資期貨未平倉</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>32058口</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>17022口</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>結算</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>融資融券變化</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>71.39億</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>-2.77億</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>-13.85億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-5.92億</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-118.42億</t>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>None億</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -838,7 +976,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-399.46億</t>
+          <t>-146.35億</t>
         </is>
       </c>
     </row>
@@ -850,7 +988,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1997.28億</t>
+          <t>-731.75億</t>
         </is>
       </c>
     </row>
@@ -862,7 +1000,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-43.44億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -874,9 +1012,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-868.84億</t>
-        </is>
-      </c>
+          <t>None億</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -886,7 +1028,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>46.14億</t>
+          <t>30.25億</t>
         </is>
       </c>
     </row>
@@ -898,7 +1040,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>230.69億</t>
+          <t>151.27億</t>
         </is>
       </c>
     </row>
@@ -941,7 +1083,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-5.92億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -953,7 +1095,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-118.42億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -972,7 +1114,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>145.37%</t>
+          <t>None%</t>
         </is>
       </c>
     </row>
@@ -999,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1017,14 +1159,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1034,7 +1175,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1113,40 +1253,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1178,38 +1313,27 @@
         <v>505217</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>-135270</v>
+        <v>-1261</v>
       </c>
       <c r="H4" t="n">
-        <v>-330580</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3915</v>
+        <v>-256633</v>
       </c>
       <c r="J4" t="n">
-        <v>18571</v>
+        <v>4571</v>
       </c>
       <c r="K4" t="n">
-        <v>200574</v>
+        <v>107</v>
       </c>
       <c r="L4" t="n">
         <v>11351</v>
       </c>
       <c r="M4" t="n">
-        <v>41428</v>
+        <v>25511</v>
       </c>
       <c r="N4" t="n">
         <v>-4247776</v>
       </c>
-      <c r="O4" t="n">
-        <v>-5.68</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1218,41 +1342,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00708L</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S&amp;P黃金正2</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>-74</v>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>908</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>-7.82</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3905</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>-838</v>
+        <v>1021</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-173</v>
       </c>
       <c r="K5" t="n">
-        <v>3796</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>10186</v>
+        <v>2792</v>
       </c>
       <c r="M5" t="n">
-        <v>48656</v>
+        <v>8598</v>
       </c>
       <c r="N5" t="n">
-        <v>-27548</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+        <v>-78807</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1261,12 +1394,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1275,47 +1408,33 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>1255</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>-7.82</v>
+        <v>-6.34</v>
       </c>
       <c r="F6" t="n">
-        <v>3905</v>
+        <v>19185</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>-286</v>
+        <v>-1207</v>
       </c>
       <c r="H6" t="n">
-        <v>2043</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-48</v>
+        <v>-4218</v>
       </c>
       <c r="J6" t="n">
-        <v>197</v>
-      </c>
-      <c r="K6" t="n">
-        <v>345</v>
+        <v>973</v>
       </c>
       <c r="L6" t="n">
-        <v>2792</v>
+        <v>5850</v>
       </c>
       <c r="M6" t="n">
-        <v>14784</v>
+        <v>18624</v>
       </c>
       <c r="N6" t="n">
-        <v>-78807</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-10.82</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+        <v>-648977</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1324,12 +1443,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1338,47 +1457,39 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1255</v>
+        <v>1865</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-6.34</v>
+        <v>-3.62</v>
       </c>
       <c r="F7" t="n">
-        <v>19185</v>
+        <v>84647</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-1121</v>
+        <v>-5003</v>
       </c>
       <c r="H7" t="n">
-        <v>-1560</v>
+        <v>-58871</v>
       </c>
       <c r="I7" t="n">
-        <v>293</v>
+        <v>-559</v>
       </c>
       <c r="J7" t="n">
-        <v>1706</v>
+        <v>5105</v>
       </c>
       <c r="K7" t="n">
-        <v>1213</v>
+        <v>35</v>
       </c>
       <c r="L7" t="n">
-        <v>5850</v>
+        <v>22209</v>
       </c>
       <c r="M7" t="n">
-        <v>31913</v>
+        <v>67266</v>
       </c>
       <c r="N7" t="n">
-        <v>-648977</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-10.55</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+        <v>-6482962</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1387,12 +1498,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1401,47 +1512,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1865</v>
+        <v>1305</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-3.62</v>
+        <v>-8.1</v>
       </c>
       <c r="F8" t="n">
-        <v>84647</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>-27354</v>
+        <v>5102</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>423</v>
       </c>
       <c r="H8" t="n">
-        <v>-56176</v>
+        <v>-339</v>
       </c>
       <c r="I8" t="n">
-        <v>1467</v>
+        <v>123</v>
       </c>
       <c r="J8" t="n">
-        <v>9334</v>
+        <v>-161</v>
       </c>
       <c r="K8" t="n">
-        <v>4056</v>
+        <v>202</v>
       </c>
       <c r="L8" t="n">
-        <v>22209</v>
+        <v>1946</v>
       </c>
       <c r="M8" t="n">
-        <v>109996</v>
+        <v>5727</v>
       </c>
       <c r="N8" t="n">
-        <v>-6482962</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-5.67</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>-140182</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1450,12 +1553,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1464,47 +1567,39 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>104</v>
+        <v>1340</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>-7.56</v>
+        <v>-3.94</v>
       </c>
       <c r="F9" t="n">
-        <v>182140</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>38693</v>
+        <v>4739</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>-58</v>
       </c>
       <c r="H9" t="n">
-        <v>-41806</v>
+        <v>-2269</v>
       </c>
       <c r="I9" t="n">
-        <v>-5297</v>
+        <v>14</v>
       </c>
       <c r="J9" t="n">
-        <v>22589</v>
+        <v>-282</v>
       </c>
       <c r="K9" t="n">
-        <v>2809</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
-        <v>122794</v>
+        <v>2702</v>
       </c>
       <c r="M9" t="n">
-        <v>682847</v>
+        <v>6189</v>
       </c>
       <c r="N9" t="n">
-        <v>-1114155</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-13.26</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>-106283</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1536,38 +1631,30 @@
         <v>3828</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>-118</v>
+        <v>-1040</v>
       </c>
       <c r="H10" t="n">
-        <v>-68</v>
+        <v>92</v>
       </c>
       <c r="I10" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="J10" t="n">
-        <v>656</v>
+        <v>79</v>
       </c>
       <c r="K10" t="n">
-        <v>174</v>
+        <v>59</v>
       </c>
       <c r="L10" t="n">
         <v>1729</v>
       </c>
       <c r="M10" t="n">
-        <v>10297</v>
+        <v>5995</v>
       </c>
       <c r="N10" t="n">
         <v>-89507</v>
       </c>
-      <c r="O10" t="n">
-        <v>-7.75</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1576,12 +1663,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1590,47 +1677,36 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3120</v>
+        <v>2100</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>-7</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>2354</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>-490</v>
+        <v>3961</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>406</v>
-      </c>
-      <c r="I11" t="n">
-        <v>106</v>
+        <v>-538</v>
       </c>
       <c r="J11" t="n">
-        <v>222</v>
+        <v>838</v>
       </c>
       <c r="K11" t="n">
-        <v>249</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>5984</v>
+        <v>4321</v>
       </c>
       <c r="M11" t="n">
-        <v>29251</v>
+        <v>13110</v>
       </c>
       <c r="N11" t="n">
-        <v>-19737</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-9.279999999999999</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+        <v>-19128</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1639,12 +1715,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1653,47 +1729,30 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2100</v>
+        <v>4525</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>-9.869999999999999</v>
+        <v>-4.33</v>
       </c>
       <c r="F12" t="n">
-        <v>3961</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>404</v>
+        <v>343</v>
       </c>
       <c r="H12" t="n">
-        <v>-483</v>
-      </c>
-      <c r="I12" t="n">
-        <v>5</v>
+        <v>-195</v>
       </c>
       <c r="J12" t="n">
-        <v>868</v>
-      </c>
-      <c r="K12" t="n">
-        <v>93</v>
+        <v>-20</v>
       </c>
       <c r="L12" t="n">
-        <v>4321</v>
+        <v>331</v>
       </c>
       <c r="M12" t="n">
-        <v>21535</v>
+        <v>931</v>
       </c>
       <c r="N12" t="n">
-        <v>-19128</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-4.02</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8887</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1716,25 +1775,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1390</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>-5.76</v>
+        <v>2315</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>6399</v>
+        <v>2730</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>-455</v>
       </c>
       <c r="H13" t="n">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="I13" t="n">
         <v>379</v>
       </c>
       <c r="J13" t="n">
-        <v>338</v>
+        <v>479</v>
       </c>
       <c r="K13" t="n">
         <v>-71</v>
@@ -1743,20 +1802,12 @@
         <v>84</v>
       </c>
       <c r="M13" t="n">
-        <v>-362</v>
+        <v>-159</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1765,12 +1816,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1779,47 +1830,39 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>262</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>-3.32</v>
+        <v>449.5</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>16580</v>
+        <v>3871</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>1011</v>
+        <v>194</v>
       </c>
       <c r="H14" t="n">
-        <v>-11237</v>
+        <v>-475</v>
       </c>
       <c r="I14" t="n">
-        <v>-859</v>
+        <v>-645</v>
       </c>
       <c r="J14" t="n">
-        <v>-4719</v>
+        <v>1610</v>
       </c>
       <c r="K14" t="n">
-        <v>355</v>
+        <v>-70</v>
       </c>
       <c r="L14" t="n">
-        <v>622</v>
+        <v>-126</v>
       </c>
       <c r="M14" t="n">
-        <v>284</v>
+        <v>-687</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1828,12 +1871,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台新科</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1842,44 +1885,39 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>127</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>-9.609999999999999</v>
+        <v>974</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>2433</v>
+        <v>1350</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>46</v>
+        <v>873</v>
       </c>
       <c r="H15" t="n">
-        <v>-399</v>
+        <v>3860</v>
+      </c>
+      <c r="I15" t="n">
+        <v>188</v>
       </c>
       <c r="J15" t="n">
-        <v>-5</v>
+        <v>23</v>
       </c>
       <c r="K15" t="n">
-        <v>-83</v>
+        <v>-82</v>
       </c>
       <c r="L15" t="n">
-        <v>-85</v>
+        <v>-28</v>
       </c>
       <c r="M15" t="n">
-        <v>127</v>
+        <v>358</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1888,12 +1926,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1902,543 +1940,41 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>418.5</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>-9.9</v>
+        <v>1600</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>4.92</v>
       </c>
       <c r="F16" t="n">
-        <v>4583</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>194</v>
+        <v>904</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>-97</v>
       </c>
       <c r="H16" t="n">
-        <v>933</v>
+        <v>136</v>
       </c>
       <c r="I16" t="n">
-        <v>-645</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>2396</v>
+        <v>-33</v>
       </c>
       <c r="K16" t="n">
-        <v>-70</v>
+        <v>8</v>
       </c>
       <c r="L16" t="n">
-        <v>-126</v>
+        <v>-12</v>
       </c>
       <c r="M16" t="n">
-        <v>-1764</v>
+        <v>-67</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>景碩</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>284.5</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>-7.93</v>
-      </c>
-      <c r="F17" t="n">
-        <v>45624</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>1754</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-6356</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-496</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1698</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1281</v>
-      </c>
-      <c r="L17" t="n">
-        <v>17827</v>
-      </c>
-      <c r="M17" t="n">
-        <v>96262</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-113456</v>
-      </c>
-      <c r="O17" t="n">
-        <v>-9.65</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>3138</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>耀登</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>195.5</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>-9.91</v>
-      </c>
-      <c r="F18" t="n">
-        <v>6666</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>-70</v>
-      </c>
-      <c r="H18" t="n">
-        <v>983</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>40</v>
-      </c>
-      <c r="L18" t="n">
-        <v>4467</v>
-      </c>
-      <c r="M18" t="n">
-        <v>24186</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-11448</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-1.46</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>漢唐</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="E19" t="n">
-        <v>3467</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>202</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3485</v>
-      </c>
-      <c r="H19" t="n">
-        <v>455</v>
-      </c>
-      <c r="I19" t="n">
-        <v>862</v>
-      </c>
-      <c r="J19" t="n">
-        <v>271</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1979</v>
-      </c>
-      <c r="L19" t="n">
-        <v>11243</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-47572</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1305</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>-8.1</v>
-      </c>
-      <c r="E20" t="n">
-        <v>5102</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>-431</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-754</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-216</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-373</v>
-      </c>
-      <c r="J20" t="n">
-        <v>250</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1946</v>
-      </c>
-      <c r="L20" t="n">
-        <v>9453</v>
-      </c>
-      <c r="M20" t="n">
-        <v>-140182</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6640</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>均華</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>962</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E21" t="n">
-        <v>826</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>-97</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" t="n">
-        <v>6</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-27</v>
-      </c>
-      <c r="J21" t="n">
-        <v>8</v>
-      </c>
-      <c r="K21" t="n">
-        <v>-12</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-55</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>624</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2040</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>873</v>
-      </c>
-      <c r="G22" t="n">
-        <v>6793</v>
-      </c>
-      <c r="H22" t="n">
-        <v>188</v>
-      </c>
-      <c r="I22" t="n">
-        <v>211</v>
-      </c>
-      <c r="J22" t="n">
-        <v>-82</v>
-      </c>
-      <c r="K22" t="n">
-        <v>-28</v>
-      </c>
-      <c r="L22" t="n">
-        <v>31</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1340</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>-3.94</v>
-      </c>
-      <c r="E23" t="n">
-        <v>4739</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>-1082</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-3965</v>
-      </c>
-      <c r="H23" t="n">
-        <v>244</v>
-      </c>
-      <c r="I23" t="n">
-        <v>367</v>
-      </c>
-      <c r="J23" t="n">
-        <v>78</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2702</v>
-      </c>
-      <c r="L23" t="n">
-        <v>10435</v>
-      </c>
-      <c r="M23" t="n">
-        <v>-106283</v>
-      </c>
-      <c r="N23" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>3030</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>德律</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>237.5</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E24" t="n">
-        <v>10896</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>-421</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2976</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-6</v>
-      </c>
-      <c r="I24" t="n">
-        <v>405</v>
-      </c>
-      <c r="J24" t="n">
-        <v>246</v>
-      </c>
-      <c r="K24" t="n">
-        <v>6962</v>
-      </c>
-      <c r="L24" t="n">
-        <v>34703</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-58841</v>
-      </c>
-      <c r="N24" t="n">
-        <v>25.22</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>4525</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>-4.33</v>
-      </c>
-      <c r="E25" t="n">
-        <v>343</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-52</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-27</v>
-      </c>
-      <c r="J25" t="n">
-        <v>18</v>
-      </c>
-      <c r="K25" t="n">
-        <v>331</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1595</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-8887</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-5</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260304.xlsx
+++ b/outputs/monitor_xlsx/20260304.xlsx
@@ -544,10 +544,6 @@
           <t>-4.35%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-4.86%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,11 +583,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -618,10 +605,6 @@
           <t>+0.59%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,10 +627,6 @@
           <t>+0.25%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,10 +649,6 @@
           <t>+0.62%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -696,10 +671,6 @@
           <t>+1.93%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,10 +693,6 @@
           <t>-10.27%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -748,10 +715,6 @@
           <t>+0.13%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -769,7 +732,6 @@
           <t>-966.15億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-146.35億</t>
@@ -807,7 +769,6 @@
           <t>67.64億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>30.25億</t>
@@ -818,8 +779,6 @@
           <t>151.27億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,15 +796,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>None%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,11 +818,6 @@
           <t>-1298.54億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -885,15 +835,11 @@
           <t>32058口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>17022口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -911,7 +857,6 @@
           <t>71.39億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-2.77億</t>
@@ -1016,10 +961,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1141,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1175,6 +1117,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1976,6 +1919,54 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>266</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1873</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>-99</v>
+      </c>
+      <c r="G17" t="n">
+        <v>151</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-135</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-140</v>
+      </c>
+      <c r="J17" t="n">
+        <v>82</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6607</v>
+      </c>
+      <c r="L17" t="n">
+        <v>33249</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-21886</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-6.99</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260304.xlsx
+++ b/outputs/monitor_xlsx/20260304.xlsx
@@ -961,7 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1238,7 +1237,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1246,36 +1245,42 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>75.59999999999999</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>-4</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>505217</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>-1261</v>
+        <v>-135270</v>
       </c>
       <c r="H4" t="n">
-        <v>-256633</v>
+        <v>-428767</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3915</v>
       </c>
       <c r="J4" t="n">
-        <v>4571</v>
+        <v>13486</v>
       </c>
       <c r="K4" t="n">
-        <v>107</v>
+        <v>200574</v>
       </c>
       <c r="L4" t="n">
         <v>11351</v>
       </c>
       <c r="M4" t="n">
-        <v>25511</v>
+        <v>45195</v>
       </c>
       <c r="N4" t="n">
         <v>-4247776</v>
       </c>
+      <c r="O4" t="n">
+        <v>0.3</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1298,36 +1303,42 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>908</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>-7.82</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="6" t="n">
         <v>3905</v>
       </c>
-      <c r="G5" s="6" t="n">
-        <v>3</v>
+      <c r="G5" s="7" t="n">
+        <v>-286</v>
       </c>
       <c r="H5" t="n">
-        <v>1021</v>
+        <v>1971</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-48</v>
       </c>
       <c r="J5" t="n">
-        <v>-173</v>
+        <v>77</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>345</v>
       </c>
       <c r="L5" t="n">
         <v>2792</v>
       </c>
       <c r="M5" t="n">
-        <v>8598</v>
+        <v>14566</v>
       </c>
       <c r="N5" t="n">
         <v>-78807</v>
       </c>
+      <c r="O5" t="n">
+        <v>-7.57</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1350,33 +1361,42 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1255</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>-6.34</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="6" t="n">
         <v>19185</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>-1207</v>
+        <v>-1121</v>
       </c>
       <c r="H6" t="n">
-        <v>-4218</v>
+        <v>-4630</v>
+      </c>
+      <c r="I6" t="n">
+        <v>293</v>
       </c>
       <c r="J6" t="n">
-        <v>973</v>
+        <v>1687</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1213</v>
       </c>
       <c r="L6" t="n">
         <v>5850</v>
       </c>
       <c r="M6" t="n">
-        <v>18624</v>
+        <v>31108</v>
       </c>
       <c r="N6" t="n">
         <v>-648977</v>
       </c>
+      <c r="O6" t="n">
+        <v>-0.97</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1399,39 +1419,42 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1865</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>-3.62</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="6" t="n">
         <v>84647</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-5003</v>
+        <v>-27354</v>
       </c>
       <c r="H7" t="n">
-        <v>-58871</v>
+        <v>-90418</v>
       </c>
       <c r="I7" t="n">
-        <v>-559</v>
+        <v>1467</v>
       </c>
       <c r="J7" t="n">
-        <v>5105</v>
+        <v>9315</v>
       </c>
       <c r="K7" t="n">
-        <v>35</v>
+        <v>4056</v>
       </c>
       <c r="L7" t="n">
         <v>22209</v>
       </c>
       <c r="M7" t="n">
-        <v>67266</v>
+        <v>111110</v>
       </c>
       <c r="N7" t="n">
         <v>-6482962</v>
       </c>
+      <c r="O7" t="n">
+        <v>0.57</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1454,39 +1477,42 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1305</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>-8.1</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="6" t="n">
         <v>5102</v>
       </c>
-      <c r="G8" s="6" t="n">
-        <v>423</v>
+      <c r="G8" s="7" t="n">
+        <v>-431</v>
       </c>
       <c r="H8" t="n">
-        <v>-339</v>
+        <v>-754</v>
       </c>
       <c r="I8" t="n">
-        <v>123</v>
+        <v>-216</v>
       </c>
       <c r="J8" t="n">
-        <v>-161</v>
+        <v>-373</v>
       </c>
       <c r="K8" t="n">
-        <v>202</v>
+        <v>250</v>
       </c>
       <c r="L8" t="n">
         <v>1946</v>
       </c>
       <c r="M8" t="n">
-        <v>5727</v>
+        <v>9453</v>
       </c>
       <c r="N8" t="n">
         <v>-140182</v>
       </c>
+      <c r="O8" t="n">
+        <v>2.25</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1509,39 +1535,42 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>1340</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>-3.94</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="6" t="n">
         <v>4739</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-58</v>
+        <v>-1082</v>
       </c>
       <c r="H9" t="n">
-        <v>-2269</v>
+        <v>-3965</v>
       </c>
       <c r="I9" t="n">
-        <v>14</v>
+        <v>244</v>
       </c>
       <c r="J9" t="n">
-        <v>-282</v>
+        <v>367</v>
       </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="L9" t="n">
         <v>2702</v>
       </c>
       <c r="M9" t="n">
-        <v>6189</v>
+        <v>10435</v>
       </c>
       <c r="N9" t="n">
         <v>-106283</v>
       </c>
+      <c r="O9" t="n">
+        <v>19.39</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1564,39 +1593,42 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>2190</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>-5.6</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>3828</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>-1040</v>
+        <v>-118</v>
       </c>
       <c r="H10" t="n">
-        <v>92</v>
+        <v>-196</v>
       </c>
       <c r="I10" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="J10" t="n">
-        <v>79</v>
+        <v>217</v>
       </c>
       <c r="K10" t="n">
-        <v>59</v>
+        <v>174</v>
       </c>
       <c r="L10" t="n">
         <v>1729</v>
       </c>
       <c r="M10" t="n">
-        <v>5995</v>
+        <v>9808</v>
       </c>
       <c r="N10" t="n">
         <v>-89507</v>
       </c>
+      <c r="O10" t="n">
+        <v>6.4</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1619,36 +1651,42 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>2100</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>-9.869999999999999</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="6" t="n">
         <v>3961</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>16</v>
+        <v>404</v>
       </c>
       <c r="H11" t="n">
-        <v>-538</v>
+        <v>-115</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
       </c>
       <c r="J11" t="n">
         <v>838</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="L11" t="n">
         <v>4321</v>
       </c>
       <c r="M11" t="n">
-        <v>13110</v>
+        <v>21617</v>
       </c>
       <c r="N11" t="n">
         <v>-19128</v>
       </c>
+      <c r="O11" t="n">
+        <v>11.94</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1671,30 +1709,42 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>4525</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>-4.33</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="6" t="n">
         <v>343</v>
       </c>
+      <c r="G12" s="6" t="n">
+        <v>24</v>
+      </c>
       <c r="H12" t="n">
-        <v>-195</v>
+        <v>-52</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-1</v>
       </c>
       <c r="J12" t="n">
-        <v>-20</v>
+        <v>-27</v>
+      </c>
+      <c r="K12" t="n">
+        <v>18</v>
       </c>
       <c r="L12" t="n">
         <v>331</v>
       </c>
       <c r="M12" t="n">
-        <v>931</v>
+        <v>1595</v>
       </c>
       <c r="N12" t="n">
         <v>-8887</v>
       </c>
+      <c r="O12" t="n">
+        <v>0.11</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1717,26 +1767,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="7" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>-455</v>
       </c>
       <c r="H13" t="n">
-        <v>340</v>
+        <v>-166</v>
       </c>
       <c r="I13" t="n">
         <v>379</v>
       </c>
       <c r="J13" t="n">
-        <v>479</v>
+        <v>788</v>
       </c>
       <c r="K13" t="n">
         <v>-71</v>
@@ -1745,11 +1795,14 @@
         <v>84</v>
       </c>
       <c r="M13" t="n">
-        <v>-159</v>
+        <v>-285</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1772,26 +1825,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="7" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>194</v>
       </c>
       <c r="H14" t="n">
-        <v>-475</v>
+        <v>118</v>
       </c>
       <c r="I14" t="n">
         <v>-645</v>
       </c>
       <c r="J14" t="n">
-        <v>1610</v>
+        <v>1546</v>
       </c>
       <c r="K14" t="n">
         <v>-70</v>
@@ -1800,11 +1853,14 @@
         <v>-126</v>
       </c>
       <c r="M14" t="n">
-        <v>-687</v>
+        <v>-1719</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1827,26 +1883,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="6" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>873</v>
       </c>
       <c r="H15" t="n">
-        <v>3860</v>
+        <v>6793</v>
       </c>
       <c r="I15" t="n">
         <v>188</v>
       </c>
       <c r="J15" t="n">
-        <v>23</v>
+        <v>211</v>
       </c>
       <c r="K15" t="n">
         <v>-82</v>
@@ -1855,11 +1911,14 @@
         <v>-28</v>
       </c>
       <c r="M15" t="n">
-        <v>358</v>
+        <v>31</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1882,26 +1941,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="6" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>-97</v>
       </c>
       <c r="H16" t="n">
-        <v>136</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
         <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>-33</v>
+        <v>-27</v>
       </c>
       <c r="K16" t="n">
         <v>8</v>
@@ -1910,11 +1969,14 @@
         <v>-12</v>
       </c>
       <c r="M16" t="n">
-        <v>-67</v>
+        <v>-55</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1932,41 +1994,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>266</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>-8.279999999999999</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="7" t="n">
         <v>1873</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="G17" s="7" t="n">
         <v>-99</v>
       </c>
-      <c r="G17" t="n">
-        <v>151</v>
-      </c>
       <c r="H17" t="n">
+        <v>244</v>
+      </c>
+      <c r="I17" t="n">
         <v>-135</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>-140</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>82</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>6607</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>33249</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-21886</v>
       </c>
-      <c r="N17" t="n">
-        <v>-6.99</v>
+      <c r="O17" t="n">
+        <v>5.85</v>
       </c>
     </row>
   </sheetData>
